--- a/Curriculum_Manual_Test_Tracker.xlsx
+++ b/Curriculum_Manual_Test_Tracker.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>🐘 Pre-Math Concepts (Big vs Small &amp; Tall vs Short)</t>
+          <t>🐘 Big vs Small</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -632,15 +632,15 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-19, 2026-10-20, 2026-10-20, 2026-10-20, 2026-10-20, 2026-10-20</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Eliminated answer adjective hints in options (Elephant vs Mouse, Giraffe vs Turtle, Strawberry vs Watermelon, Feather vs Stone); cleaned question text clue; cleaned drag-order tokens</t>
+          <t>[2026-10-19] Eliminated answer adjective hints in options (Elephant vs Mouse, Giraffe vs Turtle, Strawberry vs Watermelon, Feather vs Stone); cleaned question text clue; cleaned drag-order tokens | [2026-10-20 Rev #2] Zero Hindi in English mode (headings, titles, badges, options, questions), removed paywall popup after worksheet completion, replaced broken Windows emojis (coin 🪙 -&gt; 💰, rock 🪨 -&gt; 🧱, feather 🪶 -&gt; 🍃) across codebase | [2026-10-20 Rev #3] Integrated Balvatika 2 Maths into Hands-on STEM Concept Labs (Big/Small, Tall/Short, Heavy/Light, 1-5 Counting, Shapes, Patterns, Colors); restyled all labs into light child-friendly pastel colors | [2026-10-20 Rev #4] Added Read-Aloud Speaker (TTS) option across all STEM Concept Labs for young kids who cannot read yet; enhanced SpeakerButton with pill style and per-item speech. | [2026-10-20 Rev #5] Designed multi-sensory Psychological Concept Arcade in Game Zone: Bubble Popper (Big vs Small, Tall vs Short), Seesaw Slam (Heavy vs Light), Hungry Animal Feeding Frenzy (Counting 1 to 5), Shape Ninja with audio-visual dopamine streaks, soundManager pop/chime/fanfare, and SpeakerButton read-aloud. | [2026-10-20 Rev #6] Restored missing Coin 💰 icon across ChampHeader, Dashboard Loot Strip, Quiz Header, Celebration Screen, and Lucky Spin. Eliminated all broken/missing Unicode 13 emojis (ladder 🪜 -&gt; tree 🌲, stool 🪑 -&gt; plant 🌱, feather 🪶 -&gt; leaf 🍃, rock 🪨 -&gt; brick 🧱, hippo 🦛 -&gt; bear 🐻) with universally supported standard emojis.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Pre-Math: Big/Small, Tall/Short, Heavy/Light comparison concepts</t>
+          <t>Pre-Math: Comparing sizes of animals, fruits, balls and vehicles</t>
         </is>
       </c>
     </row>
@@ -675,40 +675,40 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>🖐️ Numbers 1 to 5 (Counting &amp; Finger Fun)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>🦒 Tall vs Short</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-20] Added interactive Tall vs Short challenges to Game Zone Bubble Popper arcade and STEM size lab with Speaker TTS read-aloud support.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Counting objects 1 to 5, finger counting, visual quantity matching</t>
+          <t>Pre-Math: Height comparisons with giraffes, trees, buildings and ladders</t>
         </is>
       </c>
     </row>
@@ -733,40 +733,40 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>🔴 Shapes &amp; Colors (Circle, Square, Red, Blue)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>🧱 Heavy vs Light</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-20] Designed interactive Seesaw Slam arcade game in Game Zone for Heavy vs Light physics simulation with animated thud, voice guidance, and star rewards.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Basic Shapes (⭕ Circle, ⬛ Square, 🔺 Triangle) &amp; Primary Colors (Red, Blue, Yellow, Green)</t>
+          <t>Pre-Math: Weight intuition with bricks, leaves, balloons and seesaws</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>⚖️ More or Less &amp; Matching Pairs</t>
+          <t>📏 Long vs Short</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Comparing quantities (more vs less), matching related real-world pairs</t>
+          <t>Pre-Math: Length comparisons with trains, snakes, pencils and ropes</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>🧩 Visual Patterns &amp; Sorting</t>
+          <t>🌲 Thick vs Thin</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Identifying simple AB patterns (🔴 🔵 🔴 🔵) and sorting by shape &amp; color</t>
+          <t>Pre-Math: Girth comparisons with tree trunks, candles, books and crayons</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>🔤 Fun with Letters (A to M Recognition)</t>
+          <t>📦 Inside vs Outside</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Letter recognition &amp; visual identification for uppercase letters A through M</t>
+          <t>Pre-Math: Position concepts with birds in nest, toys in box and fish in bowl</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>🔡 Fun with Letters (N to Z Recognition)</t>
+          <t>🔝 Top vs Bottom</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Letter recognition &amp; visual identification for uppercase letters N through Z</t>
+          <t>Pre-Math: Vertical placement on trees, slides, stars on top &amp; roots below</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1013,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>🍎 First Phonics Sounds (A for Apple, B for Ball)</t>
+          <t>🔍 Near vs Far</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Beginning phonetic sounds with everyday familiar objects &amp; picture cues</t>
+          <t>Pre-Math: Distance intuition with puppy on lap vs Moon in sky</t>
         </is>
       </c>
     </row>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 9</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>🐶 Animal Sounds &amp; Rhymes (Woof, Moo, Meow)</t>
+          <t>🚶‍♂️ In Front of vs Behind</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Connecting animals with their sounds (Dog says Woof, Cat says Meow, Cow says Moo)</t>
+          <t>Pre-Math: Relative positioning in lines, hide-and-seek &amp; mirrors</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 10</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>👀 My Body &amp; Everyday Words</t>
+          <t>⚖️ More vs Less</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Identifying body parts (Eyes, Ears, Nose, Hands) and common daily objects</t>
+          <t>Pre-Math: Quantity comparisons with apples, balloons, juice &amp; stars</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 11</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>🥭 स्वर पहचान (अ से ई तक - अनार, आम, इमली, ईख)</t>
+          <t>👯 Same vs Different</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका: अ से अनार, आ से आम, इ से इमली, ई से ईख की सचित्र पहचान</t>
+          <t>Pre-Math: Matching identical pairs, footwear sets &amp; spotting differences</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 12</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>🦉 स्वर पहचान (उ से अः तक - उल्लू, ऊन, ऋषि)</t>
+          <t>🚫 Odd One Out</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका: उ से उल्लू, ऊ से ऊन, ऋ से ऋषि, ए से एड़ी, ओ से ओखली पहचान</t>
+          <t>Pre-Math: Logical categorization, finding the item that does not belong</t>
         </is>
       </c>
     </row>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 13</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>🖼️ चित्र देखकर पहला अक्षर पहचानो</t>
+          <t>1️⃣ Number 1: The Solo Sun &amp; Nose</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका: दिए गए चित्र को देखकर उसका पहला स्वर या व्यंजन चुनना</t>
+          <t>Number Sense: Deep recognition of 1 Sun, 1 Nose, 1 Moon &amp; digit 1</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 14</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>🦜 पशु-पक्षी व उनके नाम (गाय, हाथी, तोता, मोर)</t>
+          <t>2️⃣ Number 2: The Pair of Eyes &amp; Shoes</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका: परिचित पशु-पक्षियों की पहचान व उनके नाम</t>
+          <t>Number Sense: Recognition of 2 eyes, 2 ears, shoes pair &amp; 1+1 addition</t>
         </is>
       </c>
     </row>
@@ -1419,17 +1419,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 15</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>🍎 रंग, फल व शरीर के अंग (लाल, केला, आँख, कान)</t>
+          <t>3️⃣ Number 3: The Triangle Trio</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका: प्राथमिक रंग (लाल, पीला, हरा), सरल फल व शरीर के मुख्य अंग</t>
+          <t>Number Sense: 3 auto wheels, 3 traffic lights &amp; triangle corners</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 16</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>🔟 Numbers 1 to 10 (Counting &amp; Number Names)</t>
+          <t>4️⃣ Number 4: The Four-Legged Chair</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Counting 1 to 10, spelling One to Ten, matching quantities</t>
+          <t>Number Sense: 4 chair legs, 4 car wheels, 4 square sides &amp; 4 seasons</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 17</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>🔢 Numbers 11 to 20 &amp; Missing Numbers</t>
+          <t>5️⃣ Number 5: High Five Hand</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Counting 11 to 20, finding missing numbers in sequences</t>
+          <t>Number Sense: 5 hand fingers, 5 star points, 5 senses &amp; High Five</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 18</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>↔️ Before, After &amp; In-Between Numbers</t>
+          <t>🖐️ Finger Counting &amp; Subitizing</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: What comes after, before, and between numbers up to 20</t>
+          <t>Number Sense: Finger math, instant quantity recognition &amp; gestures</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 19</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>➕ Picture Addition (Counting Together up to 10)</t>
+          <t>🎲 Dice Dots &amp; Dominoes 1 to 5</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Adding two sets of objects using picture counters (🍎 + 🍎)</t>
+          <t>Number Sense: Subitizing dice dot patterns from 1 dot to 5 dots</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 20</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>➖ Picture Subtraction (Taking Away up to 10)</t>
+          <t>🔢 The Number Train: Counting 1 to 5</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Taking away objects from a set using picture counters (🎈 - 🎈)</t>
+          <t>Number Sense: Forward counting 1 to 5, number song &amp; rocket countdown</t>
         </is>
       </c>
     </row>
@@ -1762,22 +1762,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 21</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>🔠 Uppercase &amp; Lowercase Matching (Aa to Zz)</t>
+          <t>🚂 Missing Numbers on the Track (1, 2, ?, 4, 5)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Matching capital letters to small letters (Aa, Bb, Cc...)</t>
+          <t>Number Sense: Filling missing gaps in 1 to 5 number sequences</t>
         </is>
       </c>
     </row>
@@ -1820,22 +1820,22 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 22</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>🐱 3-Letter CVC Words (Cat, Bat, Pen, Sun)</t>
+          <t>↔️ Before &amp; After in 1 to 5</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Blending CVC phonics words (a, e, i, o, u short vowel sounds)</t>
+          <t>Number Sense: What comes after, what comes before &amp; in-between (1-5)</t>
         </is>
       </c>
     </row>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 23</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>🎵 Rhyming Words (Pan-Fan, Dog-Log, Pin-Tin)</t>
+          <t>⭕ Circle Fun (Round Wheel, Coin &amp; Clock)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Identifying words with identical ending sounds</t>
+          <t>Geometry: Circular 2D shapes, 0 corners, wheels, rotis, coins &amp; clocks</t>
         </is>
       </c>
     </row>
@@ -1936,22 +1936,22 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 24</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>📖 First Sight Words (is, the, in, on, under)</t>
+          <t>⬛ Square Fun (Carrom, Window &amp; Box)</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: High-frequency sight words and basic prepositions with pictures</t>
+          <t>Geometry: 4 equal sides, 4 corners, carrom boards, bread &amp; dice faces</t>
         </is>
       </c>
     </row>
@@ -1994,55 +1994,55 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 25</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>🔄 Opposites &amp; Picture Reading (Hot/Cold, Up/Down)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Tested &amp; Updated</t>
+          <t>🔺 Triangle Fun (Samosa, Pizza Slice &amp; Party Hat)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Sanitized opposite questions (Cheetah &amp; Turtle, Rock &amp; Feather) so adjectives are not leaked in options</t>
+          <t>Pending manual test</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>v1.3.18 (Build 37)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Everyday antonym pairs (Hot/Cold, Happy/Sad, Big/Small)</t>
+          <t>Geometry: 3 straight sides, 3 corners, samosas, pizza slices &amp; party hats</t>
         </is>
       </c>
     </row>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 26</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>🍇 संपूर्ण स्वर (अ से अः की पहचान)</t>
+          <t>▬ Rectangle &amp; Shapes Around Us</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका 3: सभी 13 स्वरों का सही क्रम, मौखिक उच्चारण व सचित्र पहचान</t>
+          <t>Geometry: 2 long &amp; 2 short sides, doors, smartphones, books &amp; bank notes</t>
         </is>
       </c>
     </row>
@@ -2110,22 +2110,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 27</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>🕊️ व्यंजन पहचान (क से ङ - कबूतर, खरगोश, गमला, घर)</t>
+          <t>🔄 Rolling vs Sliding</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका 3: क, ख, ग, घ, ङ की पहचान, उच्चारण व सचित्र संबंध</t>
+          <t>Spatial Physics: Round objects roll, flat objects slide, coins &amp; cans do both</t>
         </is>
       </c>
     </row>
@@ -2168,22 +2168,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 28</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>🪁 व्यंजन पहचान (च से ज्ञ - चम्मच, टमाटर, पतंग, नल)</t>
+          <t>🔴 Primary Colors (Red, Yellow, Blue &amp; Green)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका 3: च से ज्ञ तक के प्रमुख व्यंजनों की सचित्र पहचान</t>
+          <t>Colors: Red apples, yellow bananas, blue sky, green leaves &amp; color mixing</t>
         </is>
       </c>
     </row>
@@ -2226,22 +2226,22 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 29</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>🏠 दो अक्षर वाले सरल अमात्रिक शब्द (घर, जल, फल, बस)</t>
+          <t>🧩 Repeating AB Patterns</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका 3: बिना मात्रा के दो अक्षरों को जोड़कर सरल शब्द पढ़ना</t>
+          <t>Patterns: Alternating color, shape, size &amp; day/night repeating sequences</t>
         </is>
       </c>
     </row>
@@ -2284,22 +2284,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 30</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>☀️ चित्र मिलान व सरल विलोम (दिन/रात, बड़ा/छोटा)</t>
+          <t>🏆 Super Kid Pre-Math Olympiad</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>बाल वाटिका 3: चित्रों का शब्दों से मिलान व बुनियादी विलोम शब्द</t>
+          <t>Mastery: Grand milestone test across all pre-math, number 1-5 &amp; shape skills</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>🐱 Finding the Furry Cat (Shapes &amp; Space)</t>
+          <t>🔤 Fun with Letters (A to M Recognition)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Removed repeated 'is BIGGER' and 'is SMALLER' from options; removed 'Tiny' from animal sorting drag options</t>
+          <t>[2026-10-20] Initiated LKG English curriculum: Built Alphabet &amp; Phonics STEM Lab (A-M soundboard + audio mission quiz), created Alphabet Pop arcade game in Game Zone, verified 15-question progressive worksheet with zero Hindi in English mode, SpeakerButton read-aloud TTS, and golden coin rewards.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Inside/Outside, Bigger/Smaller, Rolling/Sliding</t>
+          <t>Letter recognition &amp; visual identification for uppercase letters A through M</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2415,40 +2415,40 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>📏 What is Long? What is Round?</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Tested &amp; Updated</t>
+          <t>🔡 Fun with Letters (N to Z Recognition)</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Cleaned 'Cricket Bat is LONG' and 'Round Coin' from options to avoid answer giveaways</t>
+          <t>Pending manual test</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>v1.3.18 (Build 37)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Identifying round objects vs long objects</t>
+          <t>Letter recognition &amp; visual identification for uppercase letters N through Z</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>🥭 Mango Treats (Numbers 1 to 9)</t>
+          <t>🍎 First Phonics Sounds (A for Apple, B for Ball)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Counting objects 1 to 9 &amp; concept of Zero</t>
+          <t>Beginning phonetic sounds with everyday familiar objects &amp; picture cues</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>🔟 Making Ten (Numbers 10 to 20)</t>
+          <t>🐶 Animal Sounds &amp; Rhymes (Woof, Moo, Meow)</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Bundles of 10, Tens and Ones place concept</t>
+          <t>Connecting animals with their sounds (Dog says Woof, Cat says Meow, Cow says Moo)</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>➕ How Many? (Addition up to 9)</t>
+          <t>👀 My Body &amp; Everyday Words</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Putting together, counting forward</t>
+          <t>Identifying body parts (Eyes, Ears, Nose, Hands) and common daily objects</t>
         </is>
       </c>
     </row>
@@ -2632,22 +2632,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>🥕 Vegetable Farm (Subtraction up to 9)</t>
+          <t>🥭 स्वर पहचान (अ से ई तक - अनार, आम, इमली, ईख)</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Taking away objects, how many left over?</t>
+          <t>बाल वाटिका: अ से अनार, आ से आम, इ से इमली, ई से ईख की सचित्र पहचान</t>
         </is>
       </c>
     </row>
@@ -2690,55 +2690,55 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>📐 Lina's Family (Measurement)</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Tested &amp; Updated</t>
+          <t>🦉 स्वर पहचान (उ से अः तक - उल्लू, ऊन, ऋषि)</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Eliminated answer giveaway adjectives (is TALLER, is the TALLEST, is HEAVIER, is LIGHTER, is THICKER, is THINNER) across all 8 measurement questions</t>
+          <t>Pending manual test</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>v1.3.18 (Build 37)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Longer/Shorter, Taller/Shorter, Heavier/Lighter</t>
+          <t>बाल वाटिका: उ से उल्लू, ऊ से ऊन, ऋ से ऋषि, ए से एड़ी, ओ से ओखली पहचान</t>
         </is>
       </c>
     </row>
@@ -2748,22 +2748,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>🔢 Fun with Numbers (Numbers 21 to 99)</t>
+          <t>🖼️ चित्र देखकर पहला अक्षर पहचानो</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Counting in tens, forward &amp; backward number patterns</t>
+          <t>बाल वाटिका: दिए गए चित्र को देखकर उसका पहला स्वर या व्यंजन चुनना</t>
         </is>
       </c>
     </row>
@@ -2806,22 +2806,22 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ch 9</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>🟡 Utsav (Patterns)</t>
+          <t>🦜 पशु-पक्षी व उनके नाम (गाय, हाथी, तोता, मोर)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Shapes, color &amp; sequence pattern rules</t>
+          <t>बाल वाटिका: परिचित पशु-पक्षियों की पहचान व उनके नाम</t>
         </is>
       </c>
     </row>
@@ -2864,22 +2864,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ch 10</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>⏰ How do I Spend My Day? (Time)</t>
+          <t>🍎 रंग, फल व शरीर के अंग (लाल, केला, आँख, कान)</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Morning, Afternoon, Evening, Night &amp; activity order</t>
+          <t>बाल वाटिका: प्राथमिक रंग (लाल, पीला, हरा), सरल फल व शरीर के मुख्य अंग</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Ch 11</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>🪙 How Much Can We Spend? (Money)</t>
+          <t>🔟 Numbers 1 to 10 (Counting &amp; Number Names)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Recognizing Indian currency coins (₹1, ₹2, ₹5, ₹10) &amp; notes</t>
+          <t>Kindergarten: Counting 1 to 10, spelling One to Ten, matching quantities</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Ch 12</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>🧸 So Many Toys! (Data Handling)</t>
+          <t>🔢 Numbers 11 to 20 &amp; Missing Numbers</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Sorting, categorizing and counting collections</t>
+          <t>Kindergarten: Counting 11 to 20, finding missing numbers in sequences</t>
         </is>
       </c>
     </row>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>🔤 My Family &amp; Fun with Letters (Phonics)</t>
+          <t>↔️ Before, After &amp; In-Between Numbers</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Letter sounds A-Z, beginning sounds</t>
+          <t>Kindergarten: What comes after, before, and between numbers up to 20</t>
         </is>
       </c>
     </row>
@@ -3096,22 +3096,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>🐶 Picture Reading &amp; Naming Words (Nouns)</t>
+          <t>➕ Picture Addition (Counting Together up to 10)</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Names of animals, birds, fruits &amp; objects</t>
+          <t>Kindergarten: Adding two sets of objects using picture counters (🍎 + 🍎)</t>
         </is>
       </c>
     </row>
@@ -3154,22 +3154,22 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>🍎 One and Many (Singular &amp; Plural)</t>
+          <t>➖ Picture Subtraction (Taking Away up to 10)</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Adding "-s" to show more than one</t>
+          <t>Kindergarten: Taking away objects from a set using picture counters (🎈 - 🎈)</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>🏃 Action Words in Play (Verbs)</t>
+          <t>🔠 Uppercase &amp; Lowercase Matching (Aa to Zz)</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Action verbs (Clap, Jump, Hop, Dance)</t>
+          <t>Kindergarten: Matching capital letters to small letters (Aa, Bb, Cc...)</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>🎨 Colors &amp; Describing Words (Adjectives)</t>
+          <t>🐱 3-Letter CVC Words (Cat, Bat, Pen, Sun)</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Colors, sizes &amp; shapes (Red, Big, Sweet)</t>
+          <t>Kindergarten: Blending CVC phonics words (a, e, i, o, u short vowel sounds)</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>📦 Position Words (In, On, Under)</t>
+          <t>🎵 Rhyming Words (Pan-Fan, Dog-Log, Pin-Tin)</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Prepositions of place</t>
+          <t>Kindergarten: Identifying words with identical ending sounds</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>👦 Pronouns (He, She, It)</t>
+          <t>📖 First Sight Words (is, the, in, on, under)</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>NCERT: He for boys, She for girls, It for things</t>
+          <t>Kindergarten: High-frequency sight words and basic prepositions with pictures</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3454,45 +3454,45 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>📖 Sentence Scramble &amp; Story Words</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>🔄 Opposites &amp; Picture Reading (Hot/Cold, Up/Down)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-19] Sanitized opposite questions (Cheetah &amp; Turtle, Rock &amp; Feather) so adjectives are not leaked in options</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Simple 3-word sentences with full stop</t>
+          <t>Kindergarten: Everyday antonym pairs (Hot/Cold, Happy/Sad, Big/Small)</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>👨‍👩‍👧 मीना का परिवार (स्वर, व्यंजन व अमात्रिक शब्द)</t>
+          <t>🍇 संपूर्ण स्वर (अ से अः की पहचान)</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>NCERT सारंगी 1: दो और तीन अक्षर वाले शब्द (घर, जल, कमल)</t>
+          <t>बाल वाटिका 3: सभी 13 स्वरों का सही क्रम, मौखिक उच्चारण व सचित्र पहचान</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>👴 दादा-दादी (आ की मात्रा - ा)</t>
+          <t>🕊️ व्यंजन पहचान (क से ङ - कबूतर, खरगोश, गमला, घर)</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>NCERT: आ की मात्रा वाले शब्द (आम, कान, बादल, छाता)</t>
+          <t>बाल वाटिका 3: क, ख, ग, घ, ङ की पहचान, उच्चारण व सचित्र संबंध</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>🦜 रीना का तोता (इ व ई की मात्रा - ि, ी)</t>
+          <t>🪁 व्यंजन पहचान (च से ज्ञ - चम्मच, टमाटर, पतंग, नल)</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>NCERT: छोटी इ व बड़ी ई की मात्रा में अंतर (दिन, तितली, हाथी)</t>
+          <t>बाल वाटिका 3: च से ज्ञ तक के प्रमुख व्यंजनों की सचित्र पहचान</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>🌙 चंदा मामा (उ व ऊ की मात्रा - ु, ू)</t>
+          <t>🏠 दो अक्षर वाले सरल अमात्रिक शब्द (घर, जल, फल, बस)</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>NCERT: छोटा उ व बड़ा ऊ की मात्रा (गुलाब, सूरज, भालू)</t>
+          <t>बाल वाटिका 3: बिना मात्रा के दो अक्षरों को जोड़कर सरल शब्द पढ़ना</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>🧸 वाह! मेरे खिलौने (ए, ऐ, ओ, औ की मात्रा)</t>
+          <t>☀️ चित्र मिलान व सरल विलोम (दिन/रात, बड़ा/छोटा)</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>NCERT: केला, सैनिक, तोता, खिलौना</t>
+          <t>बाल वाटिका 3: चित्रों का शब्दों से मिलान व बुनियादी विलोम शब्द</t>
         </is>
       </c>
     </row>
@@ -3797,50 +3797,50 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>🏷️ नाम वाले शब्द (संज्ञा परिचय)</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>🐱 Finding the Furry Cat (Shapes &amp; Space)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-19] Removed repeated 'is BIGGER' and 'is SMALLER' from options; removed 'Tiny' from animal sorting drag options</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>NCERT: व्यक्तियों, पशु-पक्षियों व वस्तुओं के नाम</t>
+          <t>NCERT: Inside/Outside, Bigger/Smaller, Rolling/Sliding</t>
         </is>
       </c>
     </row>
@@ -3855,50 +3855,50 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>↔️ उल्टे अर्थ वाले शब्द (विलोम शब्द)</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>📏 What is Long? What is Round?</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-19] Cleaned 'Cricket Bat is LONG' and 'Round Coin' from options to avoid answer giveaways</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>NCERT: बड़ा/छोटा, ऊपर/नीचे, दिन/रात</t>
+          <t>NCERT: Identifying round objects vs long objects</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>🏖️ A Day at the Beach (Counting in Groups)</t>
+          <t>🥭 Mango Treats (Numbers 1 to 9)</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Counting in pairs, tens, more than &amp; less than</t>
+          <t>NCERT: Counting objects 1 to 9 &amp; concept of Zero</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>📐 Shapes Around Us (Rolling &amp; Sliding)</t>
+          <t>🔟 Making Ten (Numbers 10 to 20)</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>NCERT: 2D &amp; 3D shapes, flat vs curved surfaces</t>
+          <t>NCERT: Bundles of 10, Tens and Ones place concept</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>💯 Fun with Numbers (Numbers up to 100)</t>
+          <t>➕ How Many? (Addition up to 9)</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Place value, tens and ones, expanded form</t>
+          <t>NCERT: Putting together, counting forward</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>➕ Shadow Story (Addition &amp; Put Together)</t>
+          <t>🥕 Vegetable Farm (Subtraction up to 9)</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>NCERT: 2-digit addition without carryover</t>
+          <t>NCERT: Taking away objects, how many left over?</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4150,45 +4150,45 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>✏️ Playing with Lines (Lines &amp; Shapes)</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
+          <t>📐 Lina's Family (Measurement)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Pending manual test</t>
+          <t>[2026-10-19] Eliminated answer giveaway adjectives (is TALLER, is the TALLEST, is HEAVIER, is LIGHTER, is THICKER, is THINNER) across all 8 measurement questions</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Standing lines, slanting lines, sleeping lines</t>
+          <t>NCERT: Longer/Shorter, Taller/Shorter, Heavier/Lighter</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>➖ Decoration for Festival (Subtraction)</t>
+          <t>🔢 Fun with Numbers (Numbers 21 to 99)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>NCERT: 2-digit subtraction stories</t>
+          <t>NCERT: Counting in tens, forward &amp; backward number patterns</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 9</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>📏 Rani's Gift (Measurement &amp; Length)</t>
+          <t>🟡 Utsav (Patterns)</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Handspans, paces &amp; simple meter measurement</t>
+          <t>NCERT: Shapes, color &amp; sequence pattern rules</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 10</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>📅 Which Season is it? (Time &amp; Months)</t>
+          <t>⏰ How do I Spend My Day? (Time)</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Days of the week, 12 months &amp; seasons</t>
+          <t>NCERT: Morning, Afternoon, Evening, Night &amp; activity order</t>
         </is>
       </c>
     </row>
@@ -4372,22 +4372,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 11</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>🏫 Welcome to School (Rhymes &amp; Phonics)</t>
+          <t>💰 How Much Can We Spend? (Money)</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>NCERT Mridang: Rhyming words, vowel blends</t>
+          <t>NCERT: Recognizing Indian currency coins (₹1, ₹2, ₹5, ₹10) &amp; notes</t>
         </is>
       </c>
     </row>
@@ -4430,22 +4430,22 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 12</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>🖼️ Picture Fun &amp; Naming Words</t>
+          <t>🧸 So Many Toys! (Data Handling)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Common nouns, places, classroom objects</t>
+          <t>NCERT: Sorting, categorizing and counting collections</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>🏃 Action Words &amp; Doing Words (Verbs)</t>
+          <t>🔤 My Family &amp; Fun with Letters (Phonics)</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Present action words (-ing words)</t>
+          <t>NCERT: Letter sounds A-Z, beginning sounds</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>👥 Pronouns (I, You, We, They)</t>
+          <t>🐶 Picture Reading &amp; Naming Words (Nouns)</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Replacing naming words with pronouns</t>
+          <t>NCERT: Names of animals, birds, fruits &amp; objects</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>🪞 Describing Words (Adjectives &amp; Opposites)</t>
+          <t>🍎 One and Many (Singular &amp; Plural)</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Opposite word pairs, color &amp; size words</t>
+          <t>NCERT: Adding "-s" to show more than one</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>📍 Position Words (Behind, In Front, Next)</t>
+          <t>🏃 Action Words in Play (Verbs)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Advanced prepositions of place</t>
+          <t>NCERT: Action verbs (Clap, Jump, Hop, Dance)</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>❓ Sentences &amp; Question Marks</t>
+          <t>🎨 Colors &amp; Describing Words (Adjectives)</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Capital letters, full stops and question marks</t>
+          <t>NCERT: Colors, sizes &amp; shapes (Red, Big, Sweet)</t>
         </is>
       </c>
     </row>
@@ -4778,22 +4778,22 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>🐪 ऊँट चला (संयुक्त व्यंजन व वर्ण ज्ञान)</t>
+          <t>📦 Position Words (In, On, Under)</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>NCERT सारंगी 2: क्ष, त्र, ज्ञ, श्र व द्वित्व व्यंजन (पत्ता, बिल्ली)</t>
+          <t>NCERT: Prepositions of place</t>
         </is>
       </c>
     </row>
@@ -4836,22 +4836,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>⚽ भालू ने खेली फुटबॉल (मात्रा पुनरावृत्ति)</t>
+          <t>👦 Pronouns (He, She, It)</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>NCERT: सभी मात्राओं का सही उच्चारण व वर्तनी</t>
+          <t>NCERT: He for boys, She for girls, It for things</t>
         </is>
       </c>
     </row>
@@ -4894,22 +4894,22 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>🐱 म्याऊँ, म्याऊँ! (नाम वाले शब्द - संज्ञा)</t>
+          <t>📖 Sentence Scramble &amp; Story Words</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>NCERT: प्राणी, वस्तु, स्थान के नाम</t>
+          <t>NCERT: Simple 3-word sentences with full stop</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>☀️ अधिक बलवान कौन? (विशेषण - कैसा/कितना)</t>
+          <t>👨‍👩‍👧 मीना का परिवार (स्वर, व्यंजन व अमात्रिक शब्द)</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>NCERT: लाल सेब, ठंडी हवा, मीठा आम</t>
+          <t>NCERT सारंगी 1: दो और तीन अक्षर वाले शब्द (घर, जल, कमल)</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>🤝 दोस्त की मदद (काम वाले शब्द - क्रिया)</t>
+          <t>👴 दादा-दादी (आ की मात्रा - ा)</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>NCERT: दौड़ना, पढ़ना, हँसना, खाना</t>
+          <t>NCERT: आ की मात्रा वाले शब्द (आम, कान, बादल, छाता)</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>📚 एक और अनेक (वचन - लड़का/लड़के)</t>
+          <t>🦜 रीना का तोता (इ व ई की मात्रा - ि, ी)</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>NCERT: एकवचन और बहुवचन की पहचान</t>
+          <t>NCERT: छोटी इ व बड़ी ई की मात्रा में अंतर (दिन, तितली, हाथी)</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Class 2</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>👫 स्त्रीलिंग और पुल्लिंग (लिंग पहचान)</t>
+          <t>🌙 चंदा मामा (उ व ऊ की मात्रा - ु, ू)</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>NCERT: राजा/रानी, मोर/मोरनी, लड़का/लड़की</t>
+          <t>NCERT: छोटा उ व बड़ा ऊ की मात्रा (गुलाब, सूरज, भालू)</t>
         </is>
       </c>
     </row>
@@ -5184,22 +5184,22 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>👁️ Where to Look From? (2D Views &amp; Shapes)</t>
+          <t>🧸 वाह! मेरे खिलौने (ए, ऐ, ओ, औ की मात्रा)</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Top, side, front view of objects &amp; dot grids</t>
+          <t>NCERT: केला, सैनिक, तोता, खिलौना</t>
         </is>
       </c>
     </row>
@@ -5242,22 +5242,22 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>🔢 Fun with Numbers (Numbers up to 1000)</t>
+          <t>🏷️ नाम वाले शब्द (संज्ञा परिचय)</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>NCERT: 3-digit numbers, place values, centuries</t>
+          <t>NCERT: व्यक्तियों, पशु-पक्षियों व वस्तुओं के नाम</t>
         </is>
       </c>
     </row>
@@ -5300,22 +5300,22 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>➕ Give and Take (Addition &amp; Subtraction)</t>
+          <t>↔️ उल्टे अर्थ वाले शब्द (विलोम शब्द)</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Adding and subtracting 3-digit numbers</t>
+          <t>NCERT: बड़ा/छोटा, ऊपर/नीचे, दिन/रात</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>📏 Long and Short (Length &amp; Meters)</t>
+          <t>🏖️ A Day at the Beach (Counting in Groups)</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Centimeters, meters, scale measurement</t>
+          <t>NCERT: Counting in pairs, tens, more than &amp; less than</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>📐 Shapes and Designs (Tangrams &amp; Edges)</t>
+          <t>📐 Shapes Around Us (Rolling &amp; Sliding)</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Edges, corners, tangram puzzles, tiling patterns</t>
+          <t>NCERT: 2D &amp; 3D shapes, flat vs curved surfaces</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>⏰ Time Goes On (Clocks &amp; Calendars)</t>
+          <t>💯 Fun with Numbers (Numbers up to 100)</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Reading clock hands, minutes, years &amp; calendar</t>
+          <t>NCERT: Place value, tens and ones, expanded form</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>⚖️ Who is Heavier? (Kilograms &amp; Grams)</t>
+          <t>➕ Shadow Story (Addition &amp; Put Together)</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Weight comparison, balance scales</t>
+          <t>NCERT: 2-digit addition without carryover</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>✖️ How Many Times? (Multiplication)</t>
+          <t>✏️ Playing with Lines (Lines &amp; Shapes)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Multiplication tables, repeated addition</t>
+          <t>NCERT: Standing lines, slanting lines, sleeping lines</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Ch 9</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>🥛 Jugs and Mugs (Litres &amp; Millilitres)</t>
+          <t>➖ Decoration for Festival (Subtraction)</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Liquid volume capacity measurement</t>
+          <t>NCERT: 2-digit subtraction stories</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Ch 10</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>🪙 Rupees and Paise (Money)</t>
+          <t>📏 Rani's Gift (Measurement &amp; Length)</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Notes, coins, adding money bills</t>
+          <t>NCERT: Handspans, paces &amp; simple meter measurement</t>
         </is>
       </c>
     </row>
@@ -5764,22 +5764,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>🔤 Rhyming Words &amp; Phonics</t>
+          <t>📅 Which Season is it? (Time &amp; Months)</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>Universal: Rhyming words, vowel sounds &amp; phonics</t>
+          <t>NCERT: Days of the week, 12 months &amp; seasons</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>🏛️ Common &amp; Proper Nouns</t>
+          <t>🏫 Welcome to School (Rhymes &amp; Phonics)</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>Universal: Names of specific cities, monuments, persons &amp; capitalization</t>
+          <t>NCERT Mridang: Rhyming words, vowel blends</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>📚 Singular and Plural (-s, -es, -ies)</t>
+          <t>🖼️ Picture Fun &amp; Naming Words</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>Universal: Box -&gt; Boxes, Baby -&gt; Babies, Leaf -&gt; Leaves</t>
+          <t>NCERT: Common nouns, places, classroom objects</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>⚙️ Helping Verbs (Is, Am, Are, Was, Were)</t>
+          <t>🏃 Action Words &amp; Doing Words (Verbs)</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>Universal: Subject-verb agreement with singular &amp; plural subjects</t>
+          <t>NCERT: Present action words (-ing words)</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>🌟 Adjectives &amp; Degrees of Comparison</t>
+          <t>👥 Pronouns (I, You, We, They)</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>Universal: Sweet, sweeter, sweetest &amp; describing words</t>
+          <t>NCERT: Replacing naming words with pronouns</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>⏳ Prepositions of Time &amp; Place</t>
+          <t>✨ Describing Words (Adjectives &amp; Opposites)</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>Universal: At, in, on, under, between, behind</t>
+          <t>NCERT: Opposite word pairs, color &amp; size words</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>🔗 Connecting Words (And, But, Because)</t>
+          <t>📍 Position Words (Behind, In Front, Next)</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>Universal: Conjunctions joining simple sentences</t>
+          <t>NCERT: Advanced prepositions of place</t>
         </is>
       </c>
     </row>
@@ -6170,22 +6170,22 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>👦 संज्ञा व उसके भेद (व्यक्तिवाचक व जातिवाचक)</t>
+          <t>❓ Sentences &amp; Question Marks</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: व्यक्तिवाचक, जातिवाचक व भाववाचक संज्ञा पहचान</t>
+          <t>NCERT: Capital letters, full stops and question marks</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>👥 सर्वनाम शब्द (मैं, हम, तुम, वह, वे)</t>
+          <t>🐪 ऊँट चला (संयुक्त व्यंजन व वर्ण ज्ञान)</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: पुरुषवाचक सर्वनाम (उत्तम, मध्यम, अन्य पुरुष)</t>
+          <t>NCERT सारंगी 2: क्ष, त्र, ज्ञ, श्र व द्वित्व व्यंजन (पत्ता, बिल्ली)</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>⏰ क्रिया व काल (भूत, वर्तमान, भविष्य)</t>
+          <t>⚽ भालू ने खेली फुटबॉल (मात्रा पुनरावृत्ति)</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: काम बताने वाले शब्द व तीनों काल (था, है, होगा)</t>
+          <t>NCERT: सभी मात्राओं का सही उच्चारण व वर्तनी</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>🔄 विलोम व पर्यायवाची शब्द</t>
+          <t>🐱 म्याऊँ, म्याऊँ! (नाम वाले शब्द - संज्ञा)</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: विपरीतार्थक (उलटे) व समानार्थक (पर्याय) शब्द</t>
+          <t>NCERT: प्राणी, वस्तु, स्थान के नाम</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>💭 मुहावरे व लोकोक्तियाँ</t>
+          <t>☀️ अधिक बलवान कौन? (विशेषण - कैसा/कितना)</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: कान भरना, आँख लगना, फूला न समाना, अँगूठा दिखाना</t>
+          <t>NCERT: लाल सेब, ठंडी हवा, मीठा आम</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Class 3</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>✍️ विराम चिह्न व शुद्ध वर्तनी</t>
+          <t>🤝 दोस्त की मदद (काम वाले शब्द - क्रिया)</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: पूर्ण विराम (।), प्रश्नवाचक (?), विस्मयादिबोधक (!) व शुद्ध शब्द</t>
+          <t>NCERT: दौड़ना, पढ़ना, हँसना, खाना</t>
         </is>
       </c>
     </row>
@@ -6518,22 +6518,22 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>🧱 Building with Bricks (Brick Patterns)</t>
+          <t>📚 एक और अनेक (वचन - लड़का/लड़के)</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Arch designs, wall patterns, 3D bricks</t>
+          <t>NCERT: एकवचन और बहुवचन की पहचान</t>
         </is>
       </c>
     </row>
@@ -6576,22 +6576,22 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 2</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>🏃 Long and Short (Kilometers &amp; Meters)</t>
+          <t>👫 स्त्रीलिंग और पुल्लिंग (लिंग पहचान)</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Marathon running, conversion of km and m</t>
+          <t>NCERT: राजा/रानी, मोर/मोरनी, लड़का/लड़की</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>🚌 A Trip to Bhopal (Word Problems &amp; Estimation)</t>
+          <t>👁️ Where to Look From? (2D Views &amp; Shapes)</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Bus tickets, boat rides, estimation math</t>
+          <t>NCERT: Top, side, front view of objects &amp; dot grids</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>⏱️ Tick-Tick-Tick (12h vs 24h Clock)</t>
+          <t>🔢 Fun with Numbers (Numbers up to 1000)</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Railway clocks, timeline of events</t>
+          <t>NCERT: 3-digit numbers, place values, centuries</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>🗺️ The Way The World Looks (3D Perspectives)</t>
+          <t>➕ Give and Take (Addition &amp; Subtraction)</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Top view vs side view of classroom &amp; park</t>
+          <t>NCERT: Adding and subtracting 3-digit numbers</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>💰 The Junk Seller (Currency &amp; Profit)</t>
+          <t>📏 Long and Short (Length &amp; Meters)</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Loans, interest, multiplication with money</t>
+          <t>NCERT: Centimeters, meters, scale measurement</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>🎡 Carts and Wheels (Circles &amp; Radius)</t>
+          <t>📐 Shapes and Designs (Tangrams &amp; Edges)</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Drawing circles, radius, center point</t>
+          <t>NCERT: Edges, corners, tangram puzzles, tiling patterns</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>🍕 Halves and Quarters (Fractions)</t>
+          <t>⏰ Time Goes On (Clocks &amp; Calendars)</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>NCERT: 1/2, 1/4, 3/4 fractional parts</t>
+          <t>NCERT: Reading clock hands, minutes, years &amp; calendar</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Ch 9</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>➗ Tables and Shares (Division)</t>
+          <t>⚖️ Who is Heavier? (Kilograms &amp; Grams)</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Long division with remainders</t>
+          <t>NCERT: Weight comparison, balance scales</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Ch 10</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>🌾 Fields and Fences (Perimeter &amp; Area)</t>
+          <t>✖️ How Many Times? (Multiplication)</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Boundary length of fields &amp; gardens</t>
+          <t>NCERT: Multiplication tables, repeated addition</t>
         </is>
       </c>
     </row>
@@ -7098,22 +7098,22 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 9</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>🔤 Articles &amp; Determiners (A, An, The)</t>
+          <t>🥛 Jugs and Mugs (Litres &amp; Millilitres)</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>Universal: Vowel sounds, indefinite vs definite articles</t>
+          <t>NCERT: Liquid volume capacity measurement</t>
         </is>
       </c>
     </row>
@@ -7156,22 +7156,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 10</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>🐑 Collective &amp; Abstract Nouns</t>
+          <t>💰 Rupees and Paise (Money)</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>Universal: Flocks, herds, prides, swarms, and abstract quality nouns</t>
+          <t>NCERT: Notes, coins, adding money bills</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>⚾ Past Tense &amp; Irregular Verbs</t>
+          <t>🔤 Rhyming Words &amp; Phonics</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>Universal: Irregular past tense (caught, flew, wrote, thought)</t>
+          <t>Universal: Rhyming words, vowel sounds &amp; phonics</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>🐢 Adverbs of Manner &amp; Time</t>
+          <t>🏛️ Common &amp; Proper Nouns</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>Universal: Slowly, quickly, happily, bravely, yesterday, soon</t>
+          <t>Universal: Names of specific cities, monuments, persons &amp; capitalization</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>🔗 Conjunctions &amp; Compound Sentences</t>
+          <t>📚 Singular and Plural (-s, -es, -ies)</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>Universal: Although, because, so, while, joining independent clauses</t>
+          <t>Universal: Box -&gt; Boxes, Baby -&gt; Babies, Leaf -&gt; Leaves</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>🧭 Prepositions &amp; Direction Words</t>
+          <t>⚙️ Helping Verbs (Is, Am, Are, Was, Were)</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>Universal: Across, through, into, toward, around, beside</t>
+          <t>Universal: Subject-verb agreement with singular &amp; plural subjects</t>
         </is>
       </c>
     </row>
@@ -7446,22 +7446,22 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>🌟 विशेषण व उसके भेद (गुणवाचक, संख्यावाचक)</t>
+          <t>🌟 Adjectives &amp; Degrees of Comparison</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: गुणवाचक, संख्यावाचक, परिमाणवाचक विशेषण</t>
+          <t>Universal: Sweet, sweeter, sweetest &amp; describing words</t>
         </is>
       </c>
     </row>
@@ -7504,22 +7504,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>👑 मुहावरे व लोकोक्तियाँ (प्रयोग व अर्थ)</t>
+          <t>⏳ Prepositions of Time &amp; Place</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: छक्के छुड़ाना, नौ दो ग्यारह होना, फूला न समाना</t>
+          <t>Universal: At, in, on, under, between, behind</t>
         </is>
       </c>
     </row>
@@ -7562,22 +7562,22 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>⏰ काल व उसके भेद (भूत, वर्तमान, भविष्य)</t>
+          <t>🔗 Connecting Words (And, But, Because)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: तीनों कालों का वाक्य में सही प्रयोग व काल परिवर्तन</t>
+          <t>Universal: Conjunctions joining simple sentences</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>👫 लिंग व वचन परिवर्तन के नियम</t>
+          <t>👦 संज्ञा व उसके भेद (व्यक्तिवाचक व जातिवाचक)</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: नदी ➔ नदियाँ, दवाई ➔ दवाइयाँ, कवयित्री, विदुषी</t>
+          <t>व्याकरण: व्यक्तिवाचक, जातिवाचक व भाववाचक संज्ञा पहचान</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>🔄 विलोम व पर्यायवाची शब्द</t>
+          <t>👥 सर्वनाम शब्द (मैं, हम, तुम, वह, वे)</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: बादल, वर्षा, पानी, अग्नि, सूर्य के समानार्थक व विलोम</t>
+          <t>व्याकरण: पुरुषवाचक सर्वनाम (उत्तम, मध्यम, अन्य पुरुष)</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Class 4</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>✍️ अनेक शब्दों के लिए एक शब्द</t>
+          <t>⏰ क्रिया व काल (भूत, वर्तमान, भविष्य)</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: जो खेती करे = किसान, जो कभी न मरे = अमर, आस्तिक</t>
+          <t>व्याकरण: काम बताने वाले शब्द व तीनों काल (था, है, होगा)</t>
         </is>
       </c>
     </row>
@@ -7794,22 +7794,22 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>🐟 The Fish Tale (Large Numbers &amp; Speed)</t>
+          <t>🔄 विलोम व पर्यायवाची शब्द</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Lakhs, Crores, Boat speed, Distance calculation</t>
+          <t>व्याकरण: विपरीतार्थक (उलटे) व समानार्थक (पर्याय) शब्द</t>
         </is>
       </c>
     </row>
@@ -7852,22 +7852,22 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>📐 Shapes and Angles (Acute, Right, Obtuse)</t>
+          <t>💭 मुहावरे व लोकोक्तियाँ</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Angle tester, Clock hand angles, Name angles</t>
+          <t>व्याकरण: कान भरना, आँख लगना, फूला न समाना, अँगूठा दिखाना</t>
         </is>
       </c>
     </row>
@@ -7910,22 +7910,22 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 3</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>⏹️ How Many Squares? (Area &amp; Perimeter Grids)</t>
+          <t>✍️ विराम चिह्न व शुद्ध वर्तनी</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Grid squares, Stamp areas, Footprint areas</t>
+          <t>व्याकरण: पूर्ण विराम (।), प्रश्नवाचक (?), विस्मयादिबोधक (!) व शुद्ध शब्द</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>🍰 Parts and Wholes (Fractions &amp; Equivalent)</t>
+          <t>🧱 Building with Bricks (Brick Patterns)</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Flag fractions, Equivalent fractions, Chocolate sharing</t>
+          <t>NCERT: Arch designs, wall patterns, 3D bricks</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>🪞 Does it Look the Same? (Symmetry &amp; Rotations)</t>
+          <t>🏃 Long and Short (Kilometers &amp; Meters)</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Mirror lines, 1/2 and 1/4 turns</t>
+          <t>NCERT: Marathon running, conversion of km and m</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>🔢 Multiples and Factors (LCM &amp; HCF)</t>
+          <t>🚌 A Trip to Bhopal (Word Problems &amp; Estimation)</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Common multiples, Factor trees</t>
+          <t>NCERT: Bus tickets, boat rides, estimation math</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>🪙 Tenths and Hundredths (Decimals &amp; Paise)</t>
+          <t>⏱️ Tick-Tick-Tick (12h vs 24h Clock)</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Millimeters to cm, Rupee decimals</t>
+          <t>NCERT: Railway clocks, timeline of events</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>📐 Area and its Boundary (Formulas)</t>
+          <t>🗺️ The Way The World Looks (3D Perspectives)</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Area = L × B, Perimeter = 2 × (L + B)</t>
+          <t>NCERT: Top view vs side view of classroom &amp; park</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Ch 9</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>📦 Boxes and Sketches (3D Nets &amp; Cubes)</t>
+          <t>💰 The Junk Seller (Currency &amp; Profit)</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Folding 2D nets into 3D open and closed boxes</t>
+          <t>NCERT: Loans, interest, multiplication with money</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Ch 10</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>🧊 How Big? How Heavy? (Volume)</t>
+          <t>🎡 Carts and Wheels (Circles &amp; Radius)</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Volume in cubic cm, water displacement</t>
+          <t>NCERT: Drawing circles, radius, center point</t>
         </is>
       </c>
     </row>
@@ -8374,22 +8374,22 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>📝 Types of Sentences &amp; Subject-Predicate</t>
+          <t>🍕 Halves and Quarters (Fractions)</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>Universal: Assertive, Interrogative, Imperative, Exclamatory &amp; Subject-Predicate</t>
+          <t>NCERT: 1/2, 1/4, 3/4 fractional parts</t>
         </is>
       </c>
     </row>
@@ -8432,22 +8432,22 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 9</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>💎 Nouns: Abstract &amp; Collective Mastery</t>
+          <t>➗ Tables and Shares (Division)</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>Universal: Forming abstract nouns from adjectives/verbs &amp; advanced collectives</t>
+          <t>NCERT: Long division with remainders</t>
         </is>
       </c>
     </row>
@@ -8490,22 +8490,22 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 10</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>⏳ Tenses: Present, Past &amp; Future (Simple &amp; Continuous)</t>
+          <t>🌾 Fields and Fences (Perimeter &amp; Area)</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>Universal: Present, past, and future tense forms and temporal agreement</t>
+          <t>NCERT: Boundary length of fields &amp; gardens</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>🔄 Active and Passive Voice</t>
+          <t>🔤 Articles &amp; Determiners (A, An, The)</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>Universal: Identifying doer vs receiver, by-agent, past participles</t>
+          <t>Universal: Vowel sounds, indefinite vs definite articles</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>💡 Idioms, Proverbs &amp; Figurative Language</t>
+          <t>🐑 Collective &amp; Abstract Nouns</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>Universal: Colorful idioms, proverbs, similes &amp; metaphors</t>
+          <t>Universal: Flocks, herds, prides, swarms, and abstract quality nouns</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>✍️ Punctuation, Quotation Marks &amp; Contractions</t>
+          <t>⚾ Past Tense &amp; Irregular Verbs</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>Universal: Direct speech inverted commas, apostrophes for possession &amp; contractions</t>
+          <t>Universal: Irregular past tense (caught, flew, wrote, thought)</t>
         </is>
       </c>
     </row>
@@ -8722,22 +8722,22 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>🧶 कारक व उनके विभक्ति चिह्न (परसर्ग)</t>
+          <t>🐢 Adverbs of Manner &amp; Time</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: कर्ता, कर्म, करण, संप्रदान, अपादान, संबंध, अधिकरण, संबोधन</t>
+          <t>Universal: Slowly, quickly, happily, bravely, yesterday, soon</t>
         </is>
       </c>
     </row>
@@ -8780,22 +8780,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>🌾 उपसर्ग व प्रत्यय (पहचान व शब्द निर्माण)</t>
+          <t>🔗 Conjunctions &amp; Compound Sentences</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: उपसर्ग (सु-, बे-, अन-, दुर्-) और प्रत्यय (-दार, -वान, -ई, -ता)</t>
+          <t>Universal: Although, because, so, while, joining independent clauses</t>
         </is>
       </c>
     </row>
@@ -8838,22 +8838,22 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>🏹 भाववाचक संज्ञा निर्माण</t>
+          <t>🧭 Prepositions &amp; Direction Words</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: जातिवाचक संज्ञा, सर्वनाम, विशेषण व क्रिया से भाववाचक संज्ञा बनाना</t>
+          <t>Universal: Across, through, into, toward, around, beside</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>🗿 क्रिया के भेद (सकर्मक व अकर्मक क्रिया)</t>
+          <t>🌟 विशेषण व उसके भेद (गुणवाचक, संख्यावाचक)</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: कर्म की पहचान, क्या/किसे प्रश्न नियम, सकर्मक व अकर्मक क्रिया</t>
+          <t>व्याकरण: गुणवाचक, संख्यावाचक, परिमाणवाचक विशेषण</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>🧵 मुहावरे, लोकोक्तियाँ व वाक्य प्रयोग</t>
+          <t>👑 मुहावरे व लोकोक्तियाँ (प्रयोग व अर्थ)</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: दाँतों तले उँगली दबाना, कमर कसना, आँखें खुलना, लोकोक्ति अर्थ</t>
+          <t>व्याकरण: छक्के छुड़ाना, नौ दो ग्यारह होना, फूला न समाना</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Class 5</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>✉️ विराम चिह्न, वर्तनी शुद्धि व वाक्य रचना</t>
+          <t>⏰ काल व उसके भेद (भूत, वर्तमान, भविष्य)</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: अल्पविराम, पूर्णविराम, उद्धरण चिह्न, शुद्ध वर्तनी व वाक्य रचना</t>
+          <t>व्याकरण: तीनों कालों का वाक्य में सही प्रयोग व काल परिवर्तन</t>
         </is>
       </c>
     </row>
@@ -9070,22 +9070,22 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>🏛️ Knowing Our Numbers (Lakhs &amp; Roman Numerals)</t>
+          <t>👫 लिंग व वचन परिवर्तन के नियम</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Indian &amp; International systems, Roman symbols</t>
+          <t>व्याकरण: नदी ➔ नदियाँ, दवाई ➔ दवाइयाँ, कवयित्री, विदुषी</t>
         </is>
       </c>
     </row>
@@ -9128,22 +9128,22 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>0️⃣ Whole Numbers &amp; Number Line</t>
+          <t>🔄 विलोम व पर्यायवाची शब्द</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Closure, Commutative &amp; Distributive properties</t>
+          <t>व्याकरण: बादल, वर्षा, पानी, अग्नि, सूर्य के समानार्थक व विलोम</t>
         </is>
       </c>
     </row>
@@ -9186,22 +9186,22 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 4</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>🔢 Playing with Numbers (Prime &amp; Composite)</t>
+          <t>✍️ अनेक शब्दों के लिए एक शब्द</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Sieve of Eratosthenes, HCF, LCM</t>
+          <t>व्याकरण: जो खेती करे = किसान, जो कभी न मरे = अमर, आस्तिक</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>📐 Basic Geometrical Ideas (Points, Lines, Polygons)</t>
+          <t>🐟 The Fish Tale (Large Numbers &amp; Speed)</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Rays, Segments, Curves, Triangles, Circles</t>
+          <t>NCERT: Lakhs, Crores, Boat speed, Distance calculation</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>❄️ Integers (Positive &amp; Negative Numbers)</t>
+          <t>📐 Shapes and Angles (Acute, Right, Obtuse)</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Number line integers, temperature &amp; elevation</t>
+          <t>NCERT: Angle tester, Clock hand angles, Name angles</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>🍰 Fractions (Operations &amp; Mixed Fractions)</t>
+          <t>⏹️ How Many Squares? (Area &amp; Perimeter Grids)</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Like/Unlike fractions, addition &amp; subtraction</t>
+          <t>NCERT: Grid squares, Stamp areas, Footprint areas</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>🪙 Decimals &amp; Place Values</t>
+          <t>🍰 Parts and Wholes (Fractions &amp; Equivalent)</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Tenths, hundredths, thousandths</t>
+          <t>NCERT: Flag fractions, Equivalent fractions, Chocolate sharing</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Ch 8</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>📊 Data Handling (Tally &amp; Bar Graphs)</t>
+          <t>🦋 Does it Look the Same? (Symmetry &amp; Rotations)</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Organizing data, drawing bar graphs</t>
+          <t>NCERT: Mirror lines, 1/2 and 1/4 turns</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Ch 9</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>📏 Mensuration (Perimeter &amp; Area)</t>
+          <t>🔢 Multiples and Factors (LCM &amp; HCF)</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Regular polygons, squares, rectangles</t>
+          <t>NCERT: Common multiples, Factor trees</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Ch 10</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>💡 Algebra (Variables &amp; Expressions)</t>
+          <t>💰 Tenths and Hundredths (Decimals &amp; Paise)</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Matchstick patterns, x and y variables</t>
+          <t>NCERT: Millimeters to cm, Rupee decimals</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Ch 11</t>
+          <t>Ch 8</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>⚖️ Ratio and Proportion (Unitary Method)</t>
+          <t>📐 Area and its Boundary (Formulas)</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Comparing quantities, unitary calculations</t>
+          <t>NCERT: Area = L × B, Perimeter = 2 × (L + B)</t>
         </is>
       </c>
     </row>
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 9</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>💎 Nouns &amp; Pronouns (Advanced Cases &amp; Relative Pronouns)</t>
+          <t>📦 Boxes and Sketches (3D Nets &amp; Cubes)</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>Universal: Nominative, objective, possessive cases &amp; relative pronouns (who, which, that)</t>
+          <t>NCERT: Folding 2D nets into 3D open and closed boxes</t>
         </is>
       </c>
     </row>
@@ -9766,22 +9766,22 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Maths</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 10</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>📝 Kinds of Sentences (Declarative, Question, Exclamatory)</t>
+          <t>🧊 How Big? How Heavy? (Volume)</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>Universal: Declarative, Interrogative, Imperative, Exclamatory &amp; transformation</t>
+          <t>NCERT: Volume in cubic cm, water displacement</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>🤝 Subject-Verb Agreement</t>
+          <t>📝 Types of Sentences &amp; Subject-Predicate</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>Universal: Singular/Plural subjects, collective subjects, either/neither rules</t>
+          <t>Universal: Assertive, Interrogative, Imperative, Exclamatory &amp; Subject-Predicate</t>
         </is>
       </c>
     </row>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>⏳ Verb Tenses (Simple, Continuous, Perfect)</t>
+          <t>💎 Nouns: Abstract &amp; Collective Mastery</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>Universal: Present, Past, Future simple, continuous, and perfect tenses</t>
+          <t>Universal: Forming abstract nouns from adjectives/verbs &amp; advanced collectives</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>📍 Prepositions and Phrasal Verbs</t>
+          <t>⏳ Tenses: Present, Past &amp; Future (Simple &amp; Continuous)</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>Universal: Prepositions of place/time/direction &amp; common phrasal verbs</t>
+          <t>Universal: Present, past, and future tense forms and temporal agreement</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Ch 6</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>💬 Direct and Indirect Speech</t>
+          <t>🔄 Active and Passive Voice</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>Universal: Reporting verbs, tense backshift, pronoun changes in reported speech</t>
+          <t>Universal: Identifying doer vs receiver, by-agent, past participles</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>🔄 Active and Passive Voice &amp; Conjunctions</t>
+          <t>💡 Idioms, Proverbs &amp; Figurative Language</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>Universal: Active to passive transformation across tenses &amp; coordinating/subordinating conjunctions</t>
+          <t>Universal: Colorful idioms, proverbs, similes &amp; metaphors</t>
         </is>
       </c>
     </row>
@@ -10114,22 +10114,22 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 6</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>🐦 संज्ञा, सर्वनाम व पद परिचय</t>
+          <t>✍️ Punctuation, Quotation Marks &amp; Contractions</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: संज्ञा के भेद, सर्वनाम के 6 भेद व वाक्य में पदों का व्याकरणिक परिचय</t>
+          <t>Universal: Direct speech inverted commas, apostrophes for possession &amp; contractions</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>🌟 विशेषण व उसके भेद (प्रविशेषण सहित)</t>
+          <t>🧶 कारक व उनके विभक्ति चिह्न (परसर्ग)</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: गुणवाचक, संख्यावाचक, परिमाणवाचक, सार्वनामिक विशेषण व प्रविशेषण</t>
+          <t>व्याकरण: कर्ता, कर्म, करण, संप्रदान, अपादान, संबंध, अधिकरण, संबोधन</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Ch 3</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>🤝 संधि परिचय (स्वर संधि के भेद)</t>
+          <t>🌾 उपसर्ग व प्रत्यय (पहचान व शब्द निर्माण)</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: दो वर्णों का मेल, दीर्घ, गुण, वृद्धि, यण व अयादि स्वर संधि नियम</t>
+          <t>व्याकरण: उपसर्ग (सु-, बे-, अन-, दुर्-) और प्रत्यय (-दार, -वान, -ई, -ता)</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Ch 4</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>🧩 उपसर्ग, प्रत्यय व शब्द निर्माण</t>
+          <t>🏹 भाववाचक संज्ञा निर्माण</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: तत्सम, तद्भव व विदेशी उपसर्ग-प्रत्यय द्वारा नवीन शब्द रचना</t>
+          <t>व्याकरण: जातिवाचक संज्ञा, सर्वनाम, विशेषण व क्रिया से भाववाचक संज्ञा बनाना</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Class 6</t>
+          <t>Class 5</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 4</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>📖 विराम चिह्न व अशुद्ध वाक्य शोधन</t>
+          <t>🗿 क्रिया के भेद (सकर्मक व अकर्मक क्रिया)</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>व्याकरण: सभी प्रमुख विराम चिह्न, लिंग, वचन, कारक व पदक्रम अशुद्धि सुधार</t>
+          <t>व्याकरण: कर्म की पहचान, क्या/किसे प्रश्न नियम, सकर्मक व अकर्मक क्रिया</t>
         </is>
       </c>
     </row>
@@ -10404,53 +10404,1503 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
+          <t>Class 5</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Ch 5</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>🧵 मुहावरे, लोकोक्तियाँ व वाक्य प्रयोग</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: दाँतों तले उँगली दबाना, कमर कसना, आँखें खुलना, लोकोक्ति अर्थ</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Ch 6</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>✉️ विराम चिह्न, वर्तनी शुद्धि व वाक्य रचना</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L172" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: अल्पविराम, पूर्णविराम, उद्धरण चिह्न, शुद्ध वर्तनी व वाक्य रचना</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
           <t>Class 6</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Ch 1</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>🏛️ Knowing Our Numbers (Lakhs &amp; Roman Numerals)</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Indian &amp; International systems, Roman symbols</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Ch 2</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>0️⃣ Whole Numbers &amp; Number Line</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Closure, Commutative &amp; Distributive properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Ch 3</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>🔢 Playing with Numbers (Prime &amp; Composite)</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Sieve of Eratosthenes, HCF, LCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Ch 4</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>📐 Basic Geometrical Ideas (Points, Lines, Polygons)</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Rays, Segments, Curves, Triangles, Circles</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Ch 5</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>❄️ Integers (Positive &amp; Negative Numbers)</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Number line integers, temperature &amp; elevation</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Ch 6</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>🍰 Fractions (Operations &amp; Mixed Fractions)</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Like/Unlike fractions, addition &amp; subtraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Ch 7</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>💰 Decimals &amp; Place Values</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Tenths, hundredths, thousandths</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Ch 8</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>📊 Data Handling (Tally &amp; Bar Graphs)</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Organizing data, drawing bar graphs</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Ch 9</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>📏 Mensuration (Perimeter &amp; Area)</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Regular polygons, squares, rectangles</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Ch 10</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>💡 Algebra (Variables &amp; Expressions)</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Matchstick patterns, x and y variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Ch 11</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>⚖️ Ratio and Proportion (Unitary Method)</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Comparing quantities, unitary calculations</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Ch 1</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>💎 Nouns &amp; Pronouns (Advanced Cases &amp; Relative Pronouns)</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L184" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Nominative, objective, possessive cases &amp; relative pronouns (who, which, that)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Ch 2</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>📝 Kinds of Sentences (Declarative, Question, Exclamatory)</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Declarative, Interrogative, Imperative, Exclamatory &amp; transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Ch 3</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>🤝 Subject-Verb Agreement</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L186" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Singular/Plural subjects, collective subjects, either/neither rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Ch 4</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Verb Tenses (Simple, Continuous, Perfect)</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Present, Past, Future simple, continuous, and perfect tenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Ch 5</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>📍 Prepositions and Phrasal Verbs</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L188" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Prepositions of place/time/direction &amp; common phrasal verbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Ch 6</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>💬 Direct and Indirect Speech</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Reporting verbs, tense backshift, pronoun changes in reported speech</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Ch 7</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>🔄 Active and Passive Voice &amp; Conjunctions</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L190" s="5" t="inlineStr">
+        <is>
+          <t>Universal: Active to passive transformation across tenses &amp; coordinating/subordinating conjunctions</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>Hindi</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Ch 1</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>🐦 संज्ञा, सर्वनाम व पद परिचय</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: संज्ञा के भेद, सर्वनाम के 6 भेद व वाक्य में पदों का व्याकरणिक परिचय</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Ch 2</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>🌟 विशेषण व उसके भेद (प्रविशेषण सहित)</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: गुणवाचक, संख्यावाचक, परिमाणवाचक, सार्वनामिक विशेषण व प्रविशेषण</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Ch 3</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>🤝 संधि परिचय (स्वर संधि के भेद)</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L193" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: दो वर्णों का मेल, दीर्घ, गुण, वृद्धि, यण व अयादि स्वर संधि नियम</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Ch 4</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>🧩 उपसर्ग, प्रत्यय व शब्द निर्माण</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L194" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: तत्सम, तद्भव व विदेशी उपसर्ग-प्रत्यय द्वारा नवीन शब्द रचना</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Ch 5</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>📖 विराम चिह्न व अशुद्ध वाक्य शोधन</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L195" s="5" t="inlineStr">
+        <is>
+          <t>व्याकरण: सभी प्रमुख विराम चिह्न, लिंग, वचन, कारक व पदक्रम अशुद्धि सुधार</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Ch 6</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>⚔️ समास परिचय व मुहावरे-लोकोक्तियाँ</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>Pending Manual Test</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="5" t="inlineStr">
-        <is>
-          <t>Pending manual test</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="5" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>Pending Manual Test</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>Pending manual test</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L196" s="5" t="inlineStr">
         <is>
           <t>व्याकरण: तत्पुरुष, द्वंद्व, द्विगु व अव्ययीभाव समास तथा प्रसिद्ध मुहावरे व लोकोक्तियाँ</t>
         </is>
@@ -10467,7 +11917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10562,12 +12012,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ch 1</t>
+          <t>Ch 2</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>🐘 Pre-Math Concepts (Big vs Small &amp; Tall vs Short)</t>
+          <t>🦒 Tall vs Short</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10577,12 +12027,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -10590,7 +12040,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Eliminated answer adjective hints in options (Elephant vs Mouse, Giraffe vs Turtle, Strawberry vs Watermelon, Feather vs Stone); cleaned question text clue; cleaned drag-order tokens</t>
+          <t>[2026-10-20] Added interactive Tall vs Short challenges to Game Zone Bubble Popper arcade and STEM size lab with Speaker TTS read-aloud support.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -10600,7 +12050,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Pre-Math: Big/Small, Tall/Short, Heavy/Light comparison concepts</t>
+          <t>Pre-Math: Height comparisons with giraffes, trees, buildings and ladders</t>
         </is>
       </c>
     </row>
@@ -10620,12 +12070,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 3</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>🧩 Visual Patterns &amp; Sorting</t>
+          <t>🧱 Heavy vs Light</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10635,12 +12085,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -10648,7 +12098,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Cleaned size pattern options from 'Big Elephant'/'Small Mouse' to clean 'Elephant'/'Mouse'</t>
+          <t>[2026-10-20] Designed interactive Seesaw Slam arcade game in Game Zone for Heavy vs Light physics simulation with animated thud, voice guidance, and star rewards.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -10658,7 +12108,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Identifying simple AB patterns (🔴 🔵 🔴 🔵) and sorting by shape &amp; color</t>
+          <t>Pre-Math: Weight intuition with bricks, leaves, balloons and seesaws</t>
         </is>
       </c>
     </row>
@@ -10668,7 +12118,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>UKG (Balvatika 3)</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -10678,12 +12128,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ch 5</t>
+          <t>Ch 1</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>🔄 Opposites &amp; Picture Reading (Hot/Cold, Up/Down)</t>
+          <t>🔤 Fun with Letters (A to M Recognition)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10693,12 +12143,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -10706,7 +12156,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Sanitized opposite questions (Cheetah &amp; Turtle, Rock &amp; Feather) so adjectives are not leaked in options</t>
+          <t>[2026-10-20] Initiated LKG English curriculum: Built Alphabet &amp; Phonics STEM Lab (A-M soundboard + audio mission quiz), created Alphabet Pop arcade game in Game Zone, verified 15-question progressive worksheet with zero Hindi in English mode, SpeakerButton read-aloud TTS, and golden coin rewards.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -10716,7 +12166,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Kindergarten: Everyday antonym pairs (Hot/Cold, Happy/Sad, Big/Small)</t>
+          <t>Letter recognition &amp; visual identification for uppercase letters A through M</t>
         </is>
       </c>
     </row>
@@ -10726,7 +12176,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -10741,7 +12191,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>🐱 Finding the Furry Cat (Shapes &amp; Space)</t>
+          <t>🐘 Big vs Small</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10756,15 +12206,15 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-19, 2026-10-20, 2026-10-20, 2026-10-20, 2026-10-20, 2026-10-20</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Removed repeated 'is BIGGER' and 'is SMALLER' from options; removed 'Tiny' from animal sorting drag options</t>
+          <t>[2026-10-19] Eliminated answer adjective hints in options (Elephant vs Mouse, Giraffe vs Turtle, Strawberry vs Watermelon, Feather vs Stone); cleaned question text clue; cleaned drag-order tokens | [2026-10-20 Rev #2] Zero Hindi in English mode (headings, titles, badges, options, questions), removed paywall popup after worksheet completion, replaced broken Windows emojis (coin 🪙 -&gt; 💰, rock 🪨 -&gt; 🧱, feather 🪶 -&gt; 🍃) across codebase | [2026-10-20 Rev #3] Integrated Balvatika 2 Maths into Hands-on STEM Concept Labs (Big/Small, Tall/Short, Heavy/Light, 1-5 Counting, Shapes, Patterns, Colors); restyled all labs into light child-friendly pastel colors | [2026-10-20 Rev #4] Added Read-Aloud Speaker (TTS) option across all STEM Concept Labs for young kids who cannot read yet; enhanced SpeakerButton with pill style and per-item speech. | [2026-10-20 Rev #5] Designed multi-sensory Psychological Concept Arcade in Game Zone: Bubble Popper (Big vs Small, Tall vs Short), Seesaw Slam (Heavy vs Light), Hungry Animal Feeding Frenzy (Counting 1 to 5), Shape Ninja with audio-visual dopamine streaks, soundManager pop/chime/fanfare, and SpeakerButton read-aloud. | [2026-10-20 Rev #6] Restored missing Coin 💰 icon across ChampHeader, Dashboard Loot Strip, Quiz Header, Celebration Screen, and Lucky Spin. Eliminated all broken/missing Unicode 13 emojis (ladder 🪜 -&gt; tree 🌲, stool 🪑 -&gt; plant 🌱, feather 🪶 -&gt; leaf 🍃, rock 🪨 -&gt; brick 🧱, hippo 🦛 -&gt; bear 🐻) with universally supported standard emojis.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -10774,7 +12224,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Inside/Outside, Bigger/Smaller, Rolling/Sliding</t>
+          <t>Pre-Math: Comparing sizes of animals, fruits, balls and vehicles</t>
         </is>
       </c>
     </row>
@@ -10784,7 +12234,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>LKG (Balvatika 2)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -10794,12 +12244,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Ch 2</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>📏 What is Long? What is Round?</t>
+          <t>🌲 Thick vs Thin</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10822,7 +12272,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>[2026-10-19] Cleaned 'Cricket Bat is LONG' and 'Round Coin' from options to avoid answer giveaways</t>
+          <t>[2026-10-19] Cleaned size pattern options from 'Big Elephant'/'Small Mouse' to clean 'Elephant'/'Mouse'</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -10832,7 +12282,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>NCERT: Identifying round objects vs long objects</t>
+          <t>Pre-Math: Girth comparisons with tree trunks, candles, books and crayons</t>
         </is>
       </c>
     </row>
@@ -10842,22 +12292,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Class 1</t>
+          <t>UKG (Balvatika 3)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Maths</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>Ch 5</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>📐 Lina's Family (Measurement)</t>
+          <t>🔄 Opposites &amp; Picture Reading (Hot/Cold, Up/Down)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10880,15 +12330,189 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
+          <t>[2026-10-19] Sanitized opposite questions (Cheetah &amp; Turtle, Rock &amp; Feather) so adjectives are not leaked in options</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>v1.3.18 (Build 37)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Kindergarten: Everyday antonym pairs (Hot/Cold, Happy/Sad, Big/Small)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ch 1</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>🐱 Finding the Furry Cat (Shapes &amp; Space)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>[2026-10-19] Removed repeated 'is BIGGER' and 'is SMALLER' from options; removed 'Tiny' from animal sorting drag options</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>v1.3.18 (Build 37)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Inside/Outside, Bigger/Smaller, Rolling/Sliding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Ch 2</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>📏 What is Long? What is Round?</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>[2026-10-19] Cleaned 'Cricket Bat is LONG' and 'Round Coin' from options to avoid answer giveaways</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>v1.3.18 (Build 37)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>NCERT: Identifying round objects vs long objects</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Maths</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ch 7</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>📐 Lina's Family (Measurement)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Tested &amp; Updated</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
           <t>[2026-10-19] Eliminated answer giveaway adjectives (is TALLER, is the TALLEST, is HEAVIER, is LIGHTER, is THICKER, is THINNER) across all 8 measurement questions</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>v1.3.18 (Build 37)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>NCERT: Longer/Shorter, Taller/Shorter, Heavier/Lighter</t>
         </is>
@@ -10955,17 +12579,17 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -11163,22 +12787,22 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>6/170 Tested</t>
+          <t>9/195 Tested</t>
         </is>
       </c>
     </row>
